--- a/Payslip_Summary.xlsx
+++ b/Payslip_Summary.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10,000.00</t>
+          <t>9,500.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10,000.00</t>
+          <t>9,500.00</t>
         </is>
       </c>
     </row>
@@ -468,15 +468,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>44.00</t>
+          <t>49.80</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.98840909090909</v>
+        <v>21.83915662650602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1,011.49</t>
+          <t>1,087.59</t>
         </is>
       </c>
     </row>
@@ -488,62 +488,62 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>143.68</v>
+        <v>136.4933333333333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>614.22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LGL_PREMIUM_AMT</t>
+          <t>nd1_reg_ot</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>114.9425</v>
+        <v>27.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>919.54</t>
+          <t>95.55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ND1_LGL_PREMIUM AMT</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>45.97636363636364</v>
+          <t>VTO_Absent</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-1,416.26</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>252.87</t>
+          <t>-1,416.26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RECRUIT</t>
+          <t>VTO_Undertime</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -551,52 +551,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>30,000.00</t>
+          <t>-407.30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30,000.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>VARIABLE INCENTIVE PLAN</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>300.00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>300.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>VTO_Absent</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>-919.54</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-919.54</t>
+          <t>-407.30</t>
         </is>
       </c>
     </row>
@@ -634,7 +594,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5,734.00</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -646,43 +606,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1,000.00</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SSS Provident</t>
+          <t>PHIC Premium</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>750.00</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PHIC Premium</t>
+          <t>HDMF Premium</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>500.00</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDMF Premium</t>
+          <t>TENDO DEDUCTION</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>200.00</t>
+          <t>1,512.50</t>
         </is>
       </c>
     </row>
@@ -719,7 +679,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41636.2</v>
+        <v>9473.799999999999</v>
       </c>
     </row>
     <row r="3">
@@ -729,7 +689,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8184</v>
+        <v>1512.5</v>
       </c>
     </row>
     <row r="4">
@@ -739,7 +699,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33452.2</v>
+        <v>7961.299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Payslip_Summary.xlsx
+++ b/Payslip_Summary.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9,500.00</t>
+          <t>10,000.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9,500.00</t>
+          <t>10,000.00</t>
         </is>
       </c>
     </row>
@@ -468,15 +468,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>49.80</t>
+          <t>55.68</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.83915662650602</v>
+        <v>22.98850574712644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1,087.59</t>
+          <t>1,280.00</t>
         </is>
       </c>
     </row>
@@ -488,42 +488,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>136.4933333333333</v>
+        <v>143.68</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>614.22</t>
+          <t>71.84</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nd1_reg_ot</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>27.3</v>
+          <t>VTO_Absent</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-919.54</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>95.55</t>
+          <t>-919.54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VTO_Absent</t>
+          <t>VTO_Undertime</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -531,32 +531,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1,416.26</t>
+          <t>-611.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1,416.26</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>VTO_Undertime</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>-407.30</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>-407.30</t>
+          <t>-611.49</t>
         </is>
       </c>
     </row>
@@ -571,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,18 +611,6 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TENDO DEDUCTION</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1,512.50</t>
         </is>
       </c>
     </row>
@@ -679,7 +647,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9473.799999999999</v>
+        <v>9820.809999999999</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +657,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1512.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -699,7 +667,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7961.299999999999</v>
+        <v>9820.809999999999</v>
       </c>
     </row>
   </sheetData>
